--- a/frontend/kskcolle/public/data/erelijsten/snelschaak.xlsx
+++ b/frontend/kskcolle/public/data/erelijsten/snelschaak.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a822bf281130dcc6/Documenten/Schaken/Website KSK Colle/_/erelijsten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="13_ncr:1_{3DAD3D53-9DED-43E3-9AE7-FA9360803884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB8E5879-4F54-49D9-A828-7B429585FBE2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC416D2D-7233-4A8A-B975-0F98ABB6C6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blitz" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="100">
   <si>
     <t>Jaar</t>
   </si>
@@ -177,6 +179,9 @@
     <t>Leander Van Gavere</t>
   </si>
   <si>
+    <t>Björn Dyckmans</t>
+  </si>
+  <si>
     <t>Rony Van Buggenhout</t>
   </si>
   <si>
@@ -279,65 +284,65 @@
     <t>Frederik De Troyer</t>
   </si>
   <si>
+    <t>Bart Kuenen</t>
+  </si>
+  <si>
+    <t>Dirk Lutz Maarten Covents</t>
+  </si>
+  <si>
+    <t>Geen Winnaar</t>
+  </si>
+  <si>
+    <t>Ronny Eelen</t>
+  </si>
+  <si>
+    <t>Johan Thoen</t>
+  </si>
+  <si>
+    <t>Dirk Janssens</t>
+  </si>
+  <si>
+    <t>Raf Van Marcke</t>
+  </si>
+  <si>
+    <t>Evert Heirbaut</t>
+  </si>
+  <si>
+    <t>Jesse Vaerendonck</t>
+  </si>
+  <si>
+    <t>Furkan Guven</t>
+  </si>
+  <si>
+    <t>Felix De Meyer</t>
+  </si>
+  <si>
+    <t>David Vertenten</t>
+  </si>
+  <si>
+    <t>Marc Cools</t>
+  </si>
+  <si>
+    <t>Pieter-Jan Orban</t>
+  </si>
+  <si>
+    <t>Nils-Oscar De Landtsheer</t>
+  </si>
+  <si>
+    <t>Gunther Coppens</t>
+  </si>
+  <si>
+    <t>Jasper Orban</t>
+  </si>
+  <si>
     <t>Meervoudige winnaars per afdeling</t>
-  </si>
-  <si>
-    <t>Björn Dyckmans</t>
-  </si>
-  <si>
-    <t>Bart Kuenen</t>
-  </si>
-  <si>
-    <t>Geen Winnaar</t>
-  </si>
-  <si>
-    <t>Ronny Eelen</t>
-  </si>
-  <si>
-    <t>Johan Thoen</t>
-  </si>
-  <si>
-    <t>Dirk Janssens</t>
-  </si>
-  <si>
-    <t>Raf Van Marcke</t>
-  </si>
-  <si>
-    <t>Evert Heirbaut</t>
-  </si>
-  <si>
-    <t>Jesse Vaerendonck</t>
-  </si>
-  <si>
-    <t>Furkan Guven</t>
-  </si>
-  <si>
-    <t>Felix De Meyer</t>
-  </si>
-  <si>
-    <t>David Vertenten</t>
-  </si>
-  <si>
-    <t>Marc Cools</t>
-  </si>
-  <si>
-    <t>Dirk Lutz Maarten Covents</t>
-  </si>
-  <si>
-    <t>Pieter-Jan Orban</t>
-  </si>
-  <si>
-    <t>Nils-Oscar De Landtsheer</t>
-  </si>
-  <si>
-    <t>Gunther Coppens</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -564,6 +569,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -575,7 +586,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -591,9 +602,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Thema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -631,7 +642,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -737,7 +748,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -879,7 +890,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -888,7 +899,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q97"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="14" customWidth="1"/>
     <col min="2" max="2" width="3.140625" style="22" customWidth="1"/>
@@ -910,7 +921,7 @@
     <col min="18" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="27" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" s="27" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -941,7 +952,7 @@
       <c r="P1" s="26"/>
       <c r="Q1" s="25"/>
     </row>
-    <row r="2" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A2" s="1"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -960,7 +971,7 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="4"/>
     </row>
-    <row r="3" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A3" s="7">
         <v>1958</v>
       </c>
@@ -983,7 +994,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A4" s="10">
         <v>1959</v>
       </c>
@@ -1006,7 +1017,7 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A5" s="7">
         <v>1960</v>
       </c>
@@ -1029,7 +1040,7 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A6" s="10">
         <v>1961</v>
       </c>
@@ -1054,7 +1065,7 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A7" s="7">
         <v>1962</v>
       </c>
@@ -1075,7 +1086,7 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A8" s="10">
         <v>1963</v>
       </c>
@@ -1100,7 +1111,7 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="6"/>
     </row>
-    <row r="9" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A9" s="7">
         <v>1964</v>
       </c>
@@ -1123,7 +1134,7 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="6"/>
     </row>
-    <row r="10" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A10" s="10">
         <v>1965</v>
       </c>
@@ -1144,7 +1155,7 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="6"/>
     </row>
-    <row r="11" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A11" s="7">
         <v>1966</v>
       </c>
@@ -1167,7 +1178,7 @@
       <c r="P11" s="5"/>
       <c r="Q11" s="6"/>
     </row>
-    <row r="12" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A12" s="10">
         <v>1967</v>
       </c>
@@ -1190,7 +1201,7 @@
       <c r="P12" s="5"/>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A13" s="7">
         <v>1968</v>
       </c>
@@ -1200,12 +1211,12 @@
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="33" t="s">
+      <c r="F13" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="35"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="37"/>
       <c r="J13" s="5"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
@@ -1215,7 +1226,7 @@
       <c r="P13" s="5"/>
       <c r="Q13" s="6"/>
     </row>
-    <row r="14" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A14" s="10">
         <v>1969</v>
       </c>
@@ -1240,7 +1251,7 @@
       <c r="P14" s="5"/>
       <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A15" s="7">
         <v>1970</v>
       </c>
@@ -1267,7 +1278,7 @@
       <c r="P15" s="5"/>
       <c r="Q15" s="6"/>
     </row>
-    <row r="16" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A16" s="10">
         <v>1971</v>
       </c>
@@ -1288,7 +1299,7 @@
       <c r="P16" s="5"/>
       <c r="Q16" s="6"/>
     </row>
-    <row r="17" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A17" s="7">
         <v>1972</v>
       </c>
@@ -1313,7 +1324,7 @@
       <c r="P17" s="5"/>
       <c r="Q17" s="6"/>
     </row>
-    <row r="18" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A18" s="10">
         <v>1973</v>
       </c>
@@ -1338,7 +1349,7 @@
       <c r="P18" s="5"/>
       <c r="Q18" s="6"/>
     </row>
-    <row r="19" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A19" s="7">
         <v>1974</v>
       </c>
@@ -1365,7 +1376,7 @@
       <c r="P19" s="5"/>
       <c r="Q19" s="6"/>
     </row>
-    <row r="20" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A20" s="10">
         <v>1975</v>
       </c>
@@ -1392,7 +1403,7 @@
       <c r="P20" s="5"/>
       <c r="Q20" s="6"/>
     </row>
-    <row r="21" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A21" s="7">
         <v>1976</v>
       </c>
@@ -1419,7 +1430,7 @@
       <c r="P21" s="5"/>
       <c r="Q21" s="6"/>
     </row>
-    <row r="22" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A22" s="10">
         <v>1977</v>
       </c>
@@ -1446,7 +1457,7 @@
       <c r="P22" s="5"/>
       <c r="Q22" s="6"/>
     </row>
-    <row r="23" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A23" s="7">
         <v>1978</v>
       </c>
@@ -1473,7 +1484,7 @@
       <c r="P23" s="5"/>
       <c r="Q23" s="6"/>
     </row>
-    <row r="24" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A24" s="10">
         <v>1979</v>
       </c>
@@ -1500,7 +1511,7 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="6"/>
     </row>
-    <row r="25" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A25" s="7">
         <v>1980</v>
       </c>
@@ -1527,7 +1538,7 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="6"/>
     </row>
-    <row r="26" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A26" s="10">
         <v>1981</v>
       </c>
@@ -1554,7 +1565,7 @@
       <c r="P26" s="5"/>
       <c r="Q26" s="6"/>
     </row>
-    <row r="27" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A27" s="7">
         <v>1982</v>
       </c>
@@ -1581,7 +1592,7 @@
       <c r="P27" s="5"/>
       <c r="Q27" s="6"/>
     </row>
-    <row r="28" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A28" s="10">
         <v>1983</v>
       </c>
@@ -1608,7 +1619,7 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="6"/>
     </row>
-    <row r="29" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A29" s="7">
         <v>1984</v>
       </c>
@@ -1635,7 +1646,7 @@
       <c r="P29" s="5"/>
       <c r="Q29" s="6"/>
     </row>
-    <row r="30" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A30" s="10">
         <v>1985</v>
       </c>
@@ -1662,7 +1673,7 @@
       <c r="P30" s="5"/>
       <c r="Q30" s="6"/>
     </row>
-    <row r="31" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A31" s="7">
         <v>1986</v>
       </c>
@@ -1689,7 +1700,7 @@
       <c r="P31" s="5"/>
       <c r="Q31" s="6"/>
     </row>
-    <row r="32" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A32" s="10">
         <v>1987</v>
       </c>
@@ -1716,7 +1727,7 @@
       <c r="P32" s="5"/>
       <c r="Q32" s="6"/>
     </row>
-    <row r="33" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A33" s="7">
         <v>1988</v>
       </c>
@@ -1743,7 +1754,7 @@
       <c r="P33" s="5"/>
       <c r="Q33" s="6"/>
     </row>
-    <row r="34" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A34" s="10">
         <v>1989</v>
       </c>
@@ -1772,7 +1783,7 @@
       <c r="P34" s="5"/>
       <c r="Q34" s="6"/>
     </row>
-    <row r="35" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A35" s="7">
         <v>1990</v>
       </c>
@@ -1801,7 +1812,7 @@
       <c r="P35" s="5"/>
       <c r="Q35" s="6"/>
     </row>
-    <row r="36" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A36" s="10">
         <v>1991</v>
       </c>
@@ -1822,7 +1833,7 @@
       <c r="J36" s="5"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="M36" s="5"/>
       <c r="N36" s="6"/>
@@ -1830,7 +1841,7 @@
       <c r="P36" s="5"/>
       <c r="Q36" s="6"/>
     </row>
-    <row r="37" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A37" s="7">
         <v>1992</v>
       </c>
@@ -1841,17 +1852,17 @@
       <c r="D37" s="5"/>
       <c r="E37" s="6"/>
       <c r="F37" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="6"/>
       <c r="I37" s="9" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="6"/>
       <c r="L37" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="6"/>
@@ -1859,7 +1870,7 @@
       <c r="P37" s="5"/>
       <c r="Q37" s="6"/>
     </row>
-    <row r="38" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A38" s="10">
         <v>1993</v>
       </c>
@@ -1870,17 +1881,17 @@
       <c r="D38" s="5"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="6"/>
       <c r="L38" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="6"/>
@@ -1888,18 +1899,18 @@
       <c r="P38" s="5"/>
       <c r="Q38" s="6"/>
     </row>
-    <row r="39" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A39" s="7">
         <v>1994</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="9" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="6"/>
       <c r="F39" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="6"/>
@@ -1909,7 +1920,7 @@
       <c r="J39" s="5"/>
       <c r="K39" s="6"/>
       <c r="L39" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="6"/>
@@ -1917,18 +1928,18 @@
       <c r="P39" s="5"/>
       <c r="Q39" s="6"/>
     </row>
-    <row r="40" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A40" s="10">
         <v>1995</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="6" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="6"/>
@@ -1946,7 +1957,7 @@
       <c r="P40" s="5"/>
       <c r="Q40" s="6"/>
     </row>
-    <row r="41" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A41" s="7">
         <v>1996</v>
       </c>
@@ -1957,7 +1968,7 @@
       <c r="D41" s="5"/>
       <c r="E41" s="6"/>
       <c r="F41" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="6"/>
@@ -1967,7 +1978,7 @@
       <c r="J41" s="5"/>
       <c r="K41" s="6"/>
       <c r="L41" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="6"/>
@@ -1975,7 +1986,7 @@
       <c r="P41" s="5"/>
       <c r="Q41" s="6"/>
     </row>
-    <row r="42" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A42" s="10">
         <v>1997</v>
       </c>
@@ -1986,17 +1997,17 @@
       <c r="D42" s="5"/>
       <c r="E42" s="6"/>
       <c r="F42" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="6"/>
       <c r="L42" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="6"/>
@@ -2004,7 +2015,7 @@
       <c r="P42" s="5"/>
       <c r="Q42" s="6"/>
     </row>
-    <row r="43" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A43" s="7">
         <v>1998</v>
       </c>
@@ -2020,12 +2031,12 @@
       <c r="G43" s="5"/>
       <c r="H43" s="6"/>
       <c r="I43" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="6"/>
       <c r="L43" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M43" s="5"/>
       <c r="N43" s="6"/>
@@ -2033,23 +2044,23 @@
       <c r="P43" s="5"/>
       <c r="Q43" s="6"/>
     </row>
-    <row r="44" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A44" s="10">
         <v>1999</v>
       </c>
       <c r="B44" s="8"/>
       <c r="C44" s="6" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="6"/>
       <c r="I44" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="6"/>
@@ -2060,7 +2071,7 @@
       <c r="P44" s="5"/>
       <c r="Q44" s="6"/>
     </row>
-    <row r="45" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A45" s="7">
         <v>2000</v>
       </c>
@@ -2076,7 +2087,7 @@
       <c r="G45" s="5"/>
       <c r="H45" s="6"/>
       <c r="I45" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="6"/>
@@ -2087,7 +2098,7 @@
       <c r="P45" s="5"/>
       <c r="Q45" s="6"/>
     </row>
-    <row r="46" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A46" s="10">
         <v>2001</v>
       </c>
@@ -2098,7 +2109,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="6"/>
@@ -2114,7 +2125,7 @@
       <c r="P46" s="5"/>
       <c r="Q46" s="6"/>
     </row>
-    <row r="47" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A47" s="7">
         <v>2002</v>
       </c>
@@ -2125,12 +2136,12 @@
       <c r="D47" s="5"/>
       <c r="E47" s="6"/>
       <c r="F47" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="6"/>
       <c r="I47" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="6"/>
@@ -2141,7 +2152,7 @@
       <c r="P47" s="5"/>
       <c r="Q47" s="6"/>
     </row>
-    <row r="48" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A48" s="10">
         <v>2003</v>
       </c>
@@ -2152,12 +2163,12 @@
       <c r="D48" s="5"/>
       <c r="E48" s="6"/>
       <c r="F48" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="6"/>
       <c r="I48" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="6"/>
@@ -2168,18 +2179,18 @@
       <c r="P48" s="5"/>
       <c r="Q48" s="6"/>
     </row>
-    <row r="49" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A49" s="7">
         <v>2004</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="6"/>
       <c r="F49" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="6"/>
@@ -2195,23 +2206,23 @@
       <c r="P49" s="5"/>
       <c r="Q49" s="6"/>
     </row>
-    <row r="50" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A50" s="10">
         <v>2005</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="6"/>
       <c r="F50" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="6"/>
       <c r="I50" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="6"/>
@@ -2222,28 +2233,28 @@
       <c r="P50" s="5"/>
       <c r="Q50" s="6"/>
     </row>
-    <row r="51" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A51" s="7">
         <v>2006</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="6"/>
       <c r="F51" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="6"/>
       <c r="I51" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="6"/>
       <c r="L51" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M51" s="5"/>
       <c r="N51" s="6"/>
@@ -2251,18 +2262,18 @@
       <c r="P51" s="5"/>
       <c r="Q51" s="6"/>
     </row>
-    <row r="52" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A52" s="10">
         <v>2007</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="6"/>
       <c r="F52" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="6"/>
@@ -2276,23 +2287,23 @@
       <c r="P52" s="5"/>
       <c r="Q52" s="6"/>
     </row>
-    <row r="53" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A53" s="7">
         <v>2008</v>
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="6"/>
       <c r="F53" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="6"/>
       <c r="I53" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="6"/>
@@ -2303,28 +2314,28 @@
       <c r="P53" s="5"/>
       <c r="Q53" s="6"/>
     </row>
-    <row r="54" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A54" s="10">
         <v>2009</v>
       </c>
       <c r="B54" s="8"/>
       <c r="C54" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="6"/>
       <c r="F54" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="6"/>
       <c r="I54" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="6"/>
       <c r="L54" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M54" s="5"/>
       <c r="N54" s="6"/>
@@ -2332,28 +2343,28 @@
       <c r="P54" s="5"/>
       <c r="Q54" s="6"/>
     </row>
-    <row r="55" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A55" s="7">
         <v>2010</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="6"/>
       <c r="F55" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="6"/>
       <c r="I55" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="6"/>
       <c r="L55" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M55" s="5"/>
       <c r="N55" s="6"/>
@@ -2361,23 +2372,23 @@
       <c r="P55" s="5"/>
       <c r="Q55" s="6"/>
     </row>
-    <row r="56" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A56" s="10">
         <v>2011</v>
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="6"/>
       <c r="F56" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="6"/>
       <c r="I56" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="6"/>
@@ -2388,23 +2399,23 @@
       <c r="P56" s="5"/>
       <c r="Q56" s="6"/>
     </row>
-    <row r="57" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A57" s="7">
         <v>2012</v>
       </c>
       <c r="B57" s="8"/>
       <c r="C57" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="6"/>
       <c r="F57" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="6"/>
       <c r="I57" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="6"/>
@@ -2415,23 +2426,23 @@
       <c r="P57" s="5"/>
       <c r="Q57" s="6"/>
     </row>
-    <row r="58" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A58" s="10">
         <v>2013</v>
       </c>
       <c r="B58" s="8"/>
       <c r="C58" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="6"/>
       <c r="F58" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="6"/>
@@ -2442,28 +2453,28 @@
       <c r="P58" s="5"/>
       <c r="Q58" s="6"/>
     </row>
-    <row r="59" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A59" s="7">
         <v>2014</v>
       </c>
       <c r="B59" s="8"/>
       <c r="C59" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="6"/>
       <c r="F59" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="6"/>
       <c r="I59" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="6"/>
       <c r="L59" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M59" s="5"/>
       <c r="N59" s="6"/>
@@ -2471,7 +2482,7 @@
       <c r="P59" s="5"/>
       <c r="Q59" s="6"/>
     </row>
-    <row r="60" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A60" s="10">
         <v>2015</v>
       </c>
@@ -2482,17 +2493,17 @@
       <c r="D60" s="5"/>
       <c r="E60" s="6"/>
       <c r="F60" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="6"/>
       <c r="I60" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="6"/>
       <c r="L60" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M60" s="5"/>
       <c r="N60" s="6"/>
@@ -2500,38 +2511,38 @@
       <c r="P60" s="5"/>
       <c r="Q60" s="6"/>
     </row>
-    <row r="61" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A61" s="7">
         <v>2016</v>
       </c>
       <c r="B61" s="8"/>
       <c r="C61" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="6"/>
       <c r="F61" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="6"/>
       <c r="I61" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="6"/>
       <c r="L61" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M61" s="5"/>
       <c r="N61" s="6"/>
       <c r="O61" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P61" s="5"/>
       <c r="Q61" s="6"/>
     </row>
-    <row r="62" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A62" s="10">
         <v>2017</v>
       </c>
@@ -2542,38 +2553,38 @@
       <c r="D62" s="5"/>
       <c r="E62" s="6"/>
       <c r="F62" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="6"/>
       <c r="I62" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J62" s="5"/>
       <c r="K62" s="6"/>
       <c r="L62" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M62" s="5"/>
       <c r="N62" s="6"/>
       <c r="O62" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P62" s="5"/>
       <c r="Q62" s="6"/>
     </row>
-    <row r="63" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A63" s="7">
         <v>2018</v>
       </c>
       <c r="B63" s="8"/>
       <c r="C63" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="6"/>
       <c r="F63" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="6"/>
@@ -2591,7 +2602,7 @@
       <c r="P63" s="5"/>
       <c r="Q63" s="6"/>
     </row>
-    <row r="64" spans="1:17" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" ht="15" thickTop="1" thickBot="1">
       <c r="A64" s="10">
         <v>2019</v>
       </c>
@@ -2607,12 +2618,12 @@
       <c r="G64" s="5"/>
       <c r="H64" s="6"/>
       <c r="I64" s="6" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J64" s="5"/>
       <c r="K64" s="6"/>
       <c r="L64" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M64" s="5"/>
       <c r="N64" s="6"/>
@@ -2620,7 +2631,7 @@
       <c r="P64" s="5"/>
       <c r="Q64" s="6"/>
     </row>
-    <row r="65" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A65" s="7">
         <v>2020</v>
       </c>
@@ -2649,7 +2660,7 @@
       <c r="P65" s="5"/>
       <c r="Q65" s="6"/>
     </row>
-    <row r="66" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A66" s="10">
         <v>2021</v>
       </c>
@@ -2670,7 +2681,7 @@
       <c r="J66" s="5"/>
       <c r="K66" s="6"/>
       <c r="L66" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M66" s="5"/>
       <c r="N66" s="6"/>
@@ -2678,7 +2689,7 @@
       <c r="P66" s="5"/>
       <c r="Q66" s="6"/>
     </row>
-    <row r="67" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A67" s="7">
         <v>2022</v>
       </c>
@@ -2707,7 +2718,7 @@
       <c r="P67" s="5"/>
       <c r="Q67" s="6"/>
     </row>
-    <row r="68" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A68" s="10">
         <v>2023</v>
       </c>
@@ -2738,13 +2749,13 @@
       <c r="P68" s="5"/>
       <c r="Q68" s="6"/>
     </row>
-    <row r="69" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A69" s="7">
         <v>2024</v>
       </c>
       <c r="B69" s="8"/>
       <c r="C69" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="6"/>
@@ -2759,70 +2770,80 @@
       <c r="J69" s="5"/>
       <c r="K69" s="6"/>
       <c r="L69" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M69" s="5"/>
       <c r="N69" s="6"/>
       <c r="O69" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P69" s="5"/>
       <c r="Q69" s="6"/>
     </row>
-    <row r="70" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A70" s="10">
         <v>2025</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="6"/>
       <c r="F70" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="6"/>
       <c r="I70" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J70" s="5"/>
       <c r="K70" s="6"/>
       <c r="L70" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M70" s="5"/>
       <c r="N70" s="6"/>
       <c r="O70" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P70" s="5"/>
       <c r="Q70" s="6"/>
     </row>
-    <row r="71" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="12"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="13"/>
-      <c r="N71" s="4"/>
-      <c r="O71" s="11"/>
+    <row r="71" spans="1:17" ht="16.5" customHeight="1">
+      <c r="A71" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B71" s="33"/>
+      <c r="C71" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D71" s="5"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G71" s="5"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J71" s="5"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="M71" s="5"/>
+      <c r="N71" s="6"/>
+      <c r="O71" s="6"/>
       <c r="P71" s="13"/>
       <c r="Q71" s="4"/>
     </row>
-    <row r="72" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="B72" s="15"/>
       <c r="C72" s="16" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D72" s="17"/>
       <c r="E72" s="15"/>
@@ -2839,7 +2860,7 @@
       <c r="P72" s="17"/>
       <c r="Q72" s="18"/>
     </row>
-    <row r="73" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A73" s="12"/>
       <c r="B73" s="18"/>
       <c r="C73" s="19"/>
@@ -2858,7 +2879,7 @@
       <c r="P73" s="17"/>
       <c r="Q73" s="18"/>
     </row>
-    <row r="74" spans="1:17" s="27" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" s="27" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A74" s="29"/>
       <c r="B74" s="28"/>
       <c r="C74" s="24" t="s">
@@ -2887,7 +2908,7 @@
       <c r="P74" s="30"/>
       <c r="Q74" s="28"/>
     </row>
-    <row r="75" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A75" s="15">
         <v>1</v>
       </c>
@@ -2917,7 +2938,7 @@
       </c>
       <c r="K75" s="4"/>
       <c r="L75" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M75" s="20">
         <f>COUNTIF($L$3:$L$71,"Dirk Stynen*")</f>
@@ -2925,7 +2946,7 @@
       </c>
       <c r="N75" s="4"/>
       <c r="O75" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P75" s="20">
         <f>COUNTIF($O$3:$O$71,"Dirk Stynen*")</f>
@@ -2933,13 +2954,13 @@
       </c>
       <c r="Q75" s="4"/>
     </row>
-    <row r="76" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A76" s="15">
         <v>2</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D76" s="20">
         <f>COUNTIF($C$3:$C$71,"Peter Verbeeren*")</f>
@@ -2963,7 +2984,7 @@
       </c>
       <c r="K76" s="4"/>
       <c r="L76" s="32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M76" s="20">
         <f>COUNTIF($L$3:$L$71,"Thomas Buys-Devillé*")</f>
@@ -2974,7 +2995,7 @@
       <c r="P76" s="11"/>
       <c r="Q76" s="4"/>
     </row>
-    <row r="77" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A77" s="15">
         <v>3</v>
       </c>
@@ -2988,7 +3009,7 @@
       </c>
       <c r="E77" s="21"/>
       <c r="F77" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G77" s="20">
         <f>COUNTIF($F$3:$F$71,"Rony Van Buggenhout*")</f>
@@ -2996,7 +3017,7 @@
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J77" s="20">
         <f>COUNTIF($I$3:$I$71,"Kamiel Goeman*")</f>
@@ -3015,7 +3036,7 @@
       <c r="P77" s="11"/>
       <c r="Q77" s="4"/>
     </row>
-    <row r="78" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A78" s="15">
         <v>4</v>
       </c>
@@ -3029,7 +3050,7 @@
       </c>
       <c r="E78" s="21"/>
       <c r="F78" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G78" s="20">
         <f>COUNTIF($F$3:$F$71,"William Overmeire*")</f>
@@ -3045,7 +3066,7 @@
       </c>
       <c r="K78" s="4"/>
       <c r="L78" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M78" s="20">
         <f>COUNTIF($L$3:$L$71,"Maarten Covents*")</f>
@@ -3056,7 +3077,7 @@
       <c r="P78" s="13"/>
       <c r="Q78" s="4"/>
     </row>
-    <row r="79" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A79" s="15">
         <v>5</v>
       </c>
@@ -3078,7 +3099,7 @@
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J79" s="20">
         <f>COUNTIF($I$3:$I$71,"Chris De Vliegher*")</f>
@@ -3092,13 +3113,13 @@
       <c r="P79" s="13"/>
       <c r="Q79" s="4"/>
     </row>
-    <row r="80" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A80" s="15">
         <v>6</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D80" s="20">
         <f>COUNTIF($C$3:$C$71,"Niels Ongena*")</f>
@@ -3106,7 +3127,7 @@
       </c>
       <c r="E80" s="21"/>
       <c r="F80" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G80" s="20">
         <f>COUNTIF($F$3:$F$71,"Dirk Lutz*")</f>
@@ -3114,11 +3135,11 @@
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J80" s="20">
         <f>COUNTIF($I$3:$I$71,"Rony Van Buggenhout*")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K80" s="4"/>
       <c r="L80" s="6"/>
@@ -3128,7 +3149,7 @@
       <c r="P80" s="13"/>
       <c r="Q80" s="4"/>
     </row>
-    <row r="81" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A81" s="15">
         <v>7</v>
       </c>
@@ -3142,7 +3163,7 @@
       </c>
       <c r="E81" s="21"/>
       <c r="F81" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G81" s="20">
         <f>COUNTIF($F$3:$F$71,"Tijs Elsen*")</f>
@@ -3150,7 +3171,7 @@
       </c>
       <c r="H81" s="4"/>
       <c r="I81" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J81" s="20">
         <f>COUNTIF($I$3:$I$71,"Géry Rotthier*")</f>
@@ -3164,13 +3185,13 @@
       <c r="P81" s="13"/>
       <c r="Q81" s="4"/>
     </row>
-    <row r="82" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A82" s="15">
         <v>8</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="11" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="D82" s="20">
         <f>COUNTIF($C$3:$C$71,"Björn Dyckmans*")</f>
@@ -3178,7 +3199,7 @@
       </c>
       <c r="E82" s="21"/>
       <c r="F82" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G82" s="20">
         <f>COUNTIF($F$3:$F$71,"Luc Heyndrickx*")</f>
@@ -3200,7 +3221,7 @@
       <c r="P82" s="13"/>
       <c r="Q82" s="4"/>
     </row>
-    <row r="83" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A83" s="15">
         <v>9</v>
       </c>
@@ -3235,7 +3256,7 @@
       <c r="P83" s="13"/>
       <c r="Q83" s="4"/>
     </row>
-    <row r="84" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A84" s="15">
         <v>10</v>
       </c>
@@ -3257,7 +3278,7 @@
       </c>
       <c r="H84" s="4"/>
       <c r="I84" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J84" s="20">
         <f>COUNTIF($I$3:$I$71,"Dirk Lutz*")</f>
@@ -3271,7 +3292,7 @@
       <c r="P84" s="13"/>
       <c r="Q84" s="4"/>
     </row>
-    <row r="85" spans="1:17" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" ht="16.5" customHeight="1">
       <c r="A85" s="15">
         <v>11</v>
       </c>
@@ -3302,11 +3323,18 @@
       <c r="P85" s="13"/>
       <c r="Q85" s="4"/>
     </row>
-    <row r="86" spans="1:17" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="12"/>
+    <row r="86" spans="1:17" ht="15" thickTop="1" thickBot="1">
+      <c r="A86" s="34">
+        <v>12</v>
+      </c>
       <c r="B86" s="2"/>
-      <c r="C86" s="11"/>
-      <c r="D86" s="13"/>
+      <c r="C86" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D86" s="20">
+        <f>COUNTIF($C$3:$C$71,"Omer Van Broeck*")</f>
+        <v>2</v>
+      </c>
       <c r="E86" s="21"/>
       <c r="F86" s="11"/>
       <c r="G86" s="13"/>
@@ -3321,7 +3349,7 @@
       <c r="P86" s="13"/>
       <c r="Q86" s="4"/>
     </row>
-    <row r="87" spans="1:17" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" ht="15" thickTop="1" thickBot="1">
       <c r="A87" s="12"/>
       <c r="B87" s="2"/>
       <c r="C87" s="11"/>
@@ -3340,7 +3368,7 @@
       <c r="P87" s="13"/>
       <c r="Q87" s="4"/>
     </row>
-    <row r="88" spans="1:17" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" ht="15" thickTop="1" thickBot="1">
       <c r="A88" s="12"/>
       <c r="B88" s="2"/>
       <c r="C88" s="11"/>
@@ -3359,7 +3387,7 @@
       <c r="P88" s="13"/>
       <c r="Q88" s="4"/>
     </row>
-    <row r="89" spans="1:17" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" ht="15" thickTop="1" thickBot="1">
       <c r="A89" s="12"/>
       <c r="B89" s="2"/>
       <c r="C89" s="11"/>
@@ -3378,7 +3406,7 @@
       <c r="P89" s="13"/>
       <c r="Q89" s="4"/>
     </row>
-    <row r="90" spans="1:17" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" ht="15" thickTop="1" thickBot="1">
       <c r="A90" s="12"/>
       <c r="B90" s="2"/>
       <c r="C90" s="11"/>
@@ -3397,7 +3425,7 @@
       <c r="P90" s="13"/>
       <c r="Q90" s="4"/>
     </row>
-    <row r="91" spans="1:17" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" ht="15" thickTop="1" thickBot="1">
       <c r="A91" s="12"/>
       <c r="B91" s="2"/>
       <c r="C91" s="11"/>
@@ -3416,7 +3444,7 @@
       <c r="P91" s="13"/>
       <c r="Q91" s="4"/>
     </row>
-    <row r="92" spans="1:17" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" ht="15" thickTop="1" thickBot="1">
       <c r="A92" s="12"/>
       <c r="B92" s="2"/>
       <c r="C92" s="11"/>
@@ -3435,7 +3463,7 @@
       <c r="P92" s="13"/>
       <c r="Q92" s="4"/>
     </row>
-    <row r="93" spans="1:17" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" ht="15" thickTop="1" thickBot="1">
       <c r="A93" s="12"/>
       <c r="B93" s="2"/>
       <c r="C93" s="11"/>
@@ -3454,7 +3482,7 @@
       <c r="P93" s="13"/>
       <c r="Q93" s="4"/>
     </row>
-    <row r="94" spans="1:17" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" ht="15" thickTop="1" thickBot="1">
       <c r="A94" s="12"/>
       <c r="B94" s="2"/>
       <c r="C94" s="11"/>
@@ -3473,7 +3501,7 @@
       <c r="P94" s="13"/>
       <c r="Q94" s="4"/>
     </row>
-    <row r="95" spans="1:17" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" ht="15" thickTop="1" thickBot="1">
       <c r="A95" s="12"/>
       <c r="B95" s="2"/>
       <c r="C95" s="11"/>
@@ -3492,7 +3520,7 @@
       <c r="P95" s="13"/>
       <c r="Q95" s="4"/>
     </row>
-    <row r="96" spans="1:17" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" ht="15" thickTop="1" thickBot="1">
       <c r="A96" s="12"/>
       <c r="B96" s="4"/>
       <c r="C96" s="11"/>
@@ -3511,7 +3539,7 @@
       <c r="P96" s="13"/>
       <c r="Q96" s="4"/>
     </row>
-    <row r="97" ht="14.25" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" thickTop="1"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F75:G85">
     <sortCondition descending="1" ref="G75:G85"/>
